--- a/medical_application_forms/030_medical_history_information_form--medical_application_forms.xlsx
+++ b/medical_application_forms/030_medical_history_information_form--medical_application_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -876,7 +876,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>heart_disease</t>
+          <t>heart disease</t>
         </is>
       </c>
     </row>
@@ -893,7 +893,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>kidney_disease</t>
+          <t>kidney disease</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>liver_disease</t>
+          <t>liver disease</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>neurological_disease</t>
+          <t>neurological disease</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>mental_health_disease</t>
+          <t>mental health disease</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>sleep_apnea</t>
+          <t>sleep apnea</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>other_medical_condition</t>
+          <t>other medical condition</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>blood_test</t>
+          <t>blood test</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>urine_test</t>
+          <t>urine test</t>
         </is>
       </c>
     </row>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ct_scan</t>
+          <t>ct scan</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>mri_scan</t>
+          <t>mri scan</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>x_ray</t>
+          <t>x ray</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ct_scan_2</t>
+          <t>ct scan 2</t>
         </is>
       </c>
     </row>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>mri_scan_2</t>
+          <t>mri scan 2</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>other_medical_test</t>
+          <t>other medical test</t>
         </is>
       </c>
     </row>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>tree_nuts</t>
+          <t>tree nuts</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>other_allergy</t>
+          <t>other allergy</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>heart_disease</t>
+          <t>heart disease</t>
         </is>
       </c>
     </row>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>mental_health_disease</t>
+          <t>mental health disease</t>
         </is>
       </c>
     </row>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>other_family_history</t>
+          <t>other family history</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>blood_transfusion</t>
+          <t>blood transfusion</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>other_medical_procedure</t>
+          <t>other medical procedure</t>
         </is>
       </c>
     </row>
